--- a/KIT-REPRISE/00-mode-d-emploi.xlsx
+++ b/KIT-REPRISE/00-mode-d-emploi.xlsx
@@ -843,7 +843,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -862,27 +862,32 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Respectez l'ordre des fichiers : certains se rattachent à des données chargées avant (accidents, trames, catalogue d'EPI).</v>
+        <v>Formats acceptés : Excel (.xlsx, .xls), LibreOffice (.ods) et CSV (séparateur point-virgule ou virgule, quel que soit l'encodage). Un document Word, PDF ou papier, ou l'export d'un autre logiciel sous un autre format, se recopie d'abord dans le modèle.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Après chaque import, l'application affiche combien de lignes ont été ajoutées, mises à jour ou ignorées : notez les lignes ignorées et corrigez-les.</v>
+        <v>Respectez l'ordre des fichiers : certains se rattachent à des données chargées avant (accidents, trames, catalogue d'EPI).</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Un fichier réimporté met à jour les lignes qu'il reconnaît ; une colonne absente du fichier ne modifie pas ce qui est déjà enregistré (Gestion RH, Dossiers AT/MP).</v>
+        <v>Après chaque import, l'application affiche combien de lignes ont été ajoutées, mises à jour ou ignorées : notez les lignes ignorées et corrigez-les.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>Un fichier réimporté met à jour les lignes qu'il reconnaît ; une colonne absente du fichier ne modifie pas ce qui est déjà enregistré (Gestion RH, Dossiers AT/MP).</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
         <v>Les données restent aujourd'hui dans le navigateur qui les importe : faites la reprise sur le poste qui servira, et gardez vos fichiers.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/KIT-REPRISE/00-mode-d-emploi.xlsx
+++ b/KIT-REPRISE/00-mode-d-emploi.xlsx
@@ -434,30 +434,30 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C2" t="str">
-        <v>Référentiels (services, sites, familles de risque…)</v>
+        <v>Comptes utilisateurs</v>
       </c>
       <c r="D2" t="str">
-        <v>Administration → Référentiels</v>
+        <v>Administration → Utilisateurs</v>
       </c>
       <c r="E2" t="str">
-        <v>À faire AVANT tout import : les colonnes « Service » des fichiers doivent reprendre exactement ces libellés.</v>
+        <v>Créés un par un (ils relèveront de la future authentification).</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Avant</v>
+        <v>00</v>
       </c>
       <c r="B3" t="str">
-        <v>(saisie à l'écran)</v>
+        <v>00-referentiels.xlsx</v>
       </c>
       <c r="C3" t="str">
-        <v>Comptes utilisateurs</v>
+        <v>Référentiels (services, familles de risque, listes)</v>
       </c>
       <c r="D3" t="str">
-        <v>Administration → Utilisateurs</v>
+        <v>Administration → Référentiels → Importer .xlsx</v>
       </c>
       <c r="E3" t="str">
-        <v>Créés un par un (ils relèveront de la future authentification).</v>
+        <v>À charger en tout premier : les colonnes « Service » des autres fichiers doivent reprendre exactement ces libellés. L'import ajoute les valeurs manquantes et n'en retire jamais ; la colonne « Définition » ne sert qu'aux familles de risque.</v>
       </c>
     </row>
     <row r="4">
@@ -474,7 +474,7 @@
         <v>Gestion RH → onglet Agents → Importer .xlsx</v>
       </c>
       <c r="E4" t="str">
-        <v>À charger en premier : les autres modules peuvent ensuite proposer ces agents dans leurs formulaires. Le responsable se désigne par son « Nom Prénom » ; il peut figurer plus bas dans le fichier.</v>
+        <v>À charger juste après les référentiels : les autres modules peuvent ensuite proposer ces agents dans leurs formulaires. Le responsable se désigne par son « Nom Prénom » ; il peut figurer plus bas dans le fichier.</v>
       </c>
     </row>
     <row r="5">
@@ -542,7 +542,7 @@
         <v>Analyse d'accident → Importer .xlsx</v>
       </c>
       <c r="E8" t="str">
-        <v>La méthode, la conclusion et les actions correctives se reprennent ; l'arbre des causes lui-même (faits, « pourquoi », diagramme d'Ishikawa) se ressaisit à l'écran — la page le signale à l'import.</v>
+        <v>La méthode, la conclusion, les actions correctives et l'arbre causal (feuilles « Faits », « Pourquoi », « Ishikawa ») se reprennent. Dans « Faits », la colonne « Découle du fait n° » désigne un autre fait de la même analyse par son numéro.</v>
       </c>
     </row>
     <row r="9">

--- a/KIT-REPRISE/00-mode-d-emploi.xlsx
+++ b/KIT-REPRISE/00-mode-d-emploi.xlsx
@@ -33,10 +33,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -400,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <cols>
     <col min="1" max="1" width="7.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -440,7 +438,7 @@
         <v>Administration → Utilisateurs</v>
       </c>
       <c r="E2" t="str">
-        <v>Créés un par un (ils relèveront de la future authentification).</v>
+        <v>Créés un par un, avec leur mot de passe et leurs profils de droits.</v>
       </c>
     </row>
     <row r="3">
@@ -751,19 +749,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>—</v>
+        <v>18</v>
       </c>
       <c r="B21" t="str">
-        <v>(saisie à l'écran)</v>
+        <v>18-plans-urgence.xlsx</v>
       </c>
       <c r="C21" t="str">
-        <v>Accueil au poste</v>
+        <v>Plans d'urgence par site</v>
       </c>
       <c r="D21" t="str">
-        <v>Accueil au poste</v>
+        <v>Situations d'urgence → onglet Plans d'urgence par site → Importer .xlsx</v>
       </c>
       <c r="E21" t="str">
-        <v>Pas d'import : les parcours se créent à l'arrivée de chaque agent.</v>
+        <v>Un plan par site. Les quatre feuilles de listes se rattachent à leur plan par « ID Plan » (ou, à défaut, par le site) ; une feuille présente remplace la liste du plan qu'elle cite.</v>
       </c>
     </row>
     <row r="22">
@@ -774,13 +772,13 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C22" t="str">
-        <v>Entreprises extérieures</v>
+        <v>Accueil au poste</v>
       </c>
       <c r="D22" t="str">
-        <v>Entreprises extérieures</v>
+        <v>Accueil au poste</v>
       </c>
       <c r="E22" t="str">
-        <v>Pas d'import : une fiche par intervention.</v>
+        <v>Pas d'import : les parcours se créent à l'arrivée de chaque agent.</v>
       </c>
     </row>
     <row r="23">
@@ -791,13 +789,13 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C23" t="str">
-        <v>Base documentaire</v>
+        <v>Entreprises extérieures</v>
       </c>
       <c r="D23" t="str">
-        <v>Base documentaire</v>
+        <v>Entreprises extérieures</v>
       </c>
       <c r="E23" t="str">
-        <v>Pas d'import : fiches et documents se saisissent à l'écran.</v>
+        <v>Pas d'import : une fiche par intervention.</v>
       </c>
     </row>
     <row r="24">
@@ -808,13 +806,13 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C24" t="str">
-        <v>Stock et lavages des EPI</v>
+        <v>Base documentaire</v>
       </c>
       <c r="D24" t="str">
-        <v>EPI &amp; Dotation</v>
+        <v>Base documentaire</v>
       </c>
       <c r="E24" t="str">
-        <v>Pas d'import pour ces deux onglets.</v>
+        <v>Pas d'import : fiches et documents se saisissent à l'écran.</v>
       </c>
     </row>
     <row r="25">
@@ -825,18 +823,35 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C25" t="str">
+        <v>Stock et lavages des EPI</v>
+      </c>
+      <c r="D25" t="str">
+        <v>EPI &amp; Dotation</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Pas d'import pour ces deux onglets.</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>—</v>
+      </c>
+      <c r="B26" t="str">
+        <v>(saisie à l'écran)</v>
+      </c>
+      <c r="C26" t="str">
         <v>Rendez-vous médicaux</v>
       </c>
-      <c r="D25" t="str">
+      <c r="D26" t="str">
         <v>Santé &amp; Visites → Agenda</v>
       </c>
-      <c r="E25" t="str">
+      <c r="E26" t="str">
         <v>Pas d'import : l'agenda démarre à la mise en service.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E26"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/KIT-REPRISE/00-mode-d-emploi.xlsx
+++ b/KIT-REPRISE/00-mode-d-emploi.xlsx
@@ -574,7 +574,7 @@
         <v>Plan d'actions → Importer .xlsx</v>
       </c>
       <c r="E10" t="str">
-        <v>Les actions saisies à la main. Celles qui découlent du Document Unique, des inspections, des analyses d'accident ou des exercices se créent toutes seules depuis ces modules : inutile de les importer ici.</v>
+        <v>Les actions saisies à la main. Celles qui découlent du Document Unique, des inspections, des analyses d'accident ou des exercices se créent toutes seules depuis ces modules : inutile de les importer ici. Les quatre colonnes d'efficacité (Efficacité, vérifiée le, par, constat) ne valent que pour une action « Fait » ; « Efficace » ou « Non efficace », sinon laisser vide.</v>
       </c>
     </row>
     <row r="11">

--- a/KIT-REPRISE/00-mode-d-emploi.xlsx
+++ b/KIT-REPRISE/00-mode-d-emploi.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <cols>
     <col min="1" max="1" width="7.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -789,13 +789,13 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C23" t="str">
-        <v>Entreprises extérieures</v>
+        <v>Signalements</v>
       </c>
       <c r="D23" t="str">
-        <v>Entreprises extérieures</v>
+        <v>Signalements</v>
       </c>
       <c r="E23" t="str">
-        <v>Pas d'import : une fiche par intervention.</v>
+        <v>Pas d'import : chaque presque-accident se signale à l'écran ; un historique se reprend au Registre AT/MP (type « Presque accident »).</v>
       </c>
     </row>
     <row r="24">
@@ -806,13 +806,13 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C24" t="str">
-        <v>Base documentaire</v>
+        <v>Entreprises extérieures</v>
       </c>
       <c r="D24" t="str">
-        <v>Base documentaire</v>
+        <v>Entreprises extérieures</v>
       </c>
       <c r="E24" t="str">
-        <v>Pas d'import : fiches et documents se saisissent à l'écran.</v>
+        <v>Pas d'import : une fiche par intervention.</v>
       </c>
     </row>
     <row r="25">
@@ -823,13 +823,13 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C25" t="str">
-        <v>Stock et lavages des EPI</v>
+        <v>Base documentaire</v>
       </c>
       <c r="D25" t="str">
-        <v>EPI &amp; Dotation</v>
+        <v>Base documentaire</v>
       </c>
       <c r="E25" t="str">
-        <v>Pas d'import pour ces deux onglets.</v>
+        <v>Pas d'import : fiches et documents se saisissent à l'écran.</v>
       </c>
     </row>
     <row r="26">
@@ -840,18 +840,35 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C26" t="str">
+        <v>Stock et lavages des EPI</v>
+      </c>
+      <c r="D26" t="str">
+        <v>EPI &amp; Dotation</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Pas d'import pour ces deux onglets.</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>—</v>
+      </c>
+      <c r="B27" t="str">
+        <v>(saisie à l'écran)</v>
+      </c>
+      <c r="C27" t="str">
         <v>Rendez-vous médicaux</v>
       </c>
-      <c r="D26" t="str">
+      <c r="D27" t="str">
         <v>Santé &amp; Visites → Agenda</v>
       </c>
-      <c r="E26" t="str">
+      <c r="E27" t="str">
         <v>Pas d'import : l'agenda démarre à la mise en service.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E27"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/KIT-REPRISE/00-mode-d-emploi.xlsx
+++ b/KIT-REPRISE/00-mode-d-emploi.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <cols>
     <col min="1" max="1" width="7.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -789,13 +789,13 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C23" t="str">
-        <v>Signalements</v>
+        <v>Revues de direction</v>
       </c>
       <c r="D23" t="str">
-        <v>Signalements</v>
+        <v>Revue de direction</v>
       </c>
       <c r="E23" t="str">
-        <v>Pas d'import : chaque presque-accident se signale à l'écran ; un historique se reprend au Registre AT/MP (type « Presque accident »).</v>
+        <v>Pas d'import : chaque revue se prépare à l'écran à partir des données reprises.</v>
       </c>
     </row>
     <row r="24">
@@ -806,13 +806,13 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C24" t="str">
-        <v>Entreprises extérieures</v>
+        <v>Signalements</v>
       </c>
       <c r="D24" t="str">
-        <v>Entreprises extérieures</v>
+        <v>Signalements</v>
       </c>
       <c r="E24" t="str">
-        <v>Pas d'import : une fiche par intervention.</v>
+        <v>Pas d'import : chaque presque-accident se signale à l'écran ; un historique se reprend au Registre AT/MP (type « Presque accident »).</v>
       </c>
     </row>
     <row r="25">
@@ -823,13 +823,13 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C25" t="str">
-        <v>Base documentaire</v>
+        <v>Entreprises extérieures</v>
       </c>
       <c r="D25" t="str">
-        <v>Base documentaire</v>
+        <v>Entreprises extérieures</v>
       </c>
       <c r="E25" t="str">
-        <v>Pas d'import : fiches et documents se saisissent à l'écran.</v>
+        <v>Pas d'import : une fiche par intervention.</v>
       </c>
     </row>
     <row r="26">
@@ -840,13 +840,13 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C26" t="str">
-        <v>Stock et lavages des EPI</v>
+        <v>Base documentaire</v>
       </c>
       <c r="D26" t="str">
-        <v>EPI &amp; Dotation</v>
+        <v>Base documentaire</v>
       </c>
       <c r="E26" t="str">
-        <v>Pas d'import pour ces deux onglets.</v>
+        <v>Pas d'import : fiches et documents se saisissent à l'écran.</v>
       </c>
     </row>
     <row r="27">
@@ -857,18 +857,35 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C27" t="str">
+        <v>Stock et lavages des EPI</v>
+      </c>
+      <c r="D27" t="str">
+        <v>EPI &amp; Dotation</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Pas d'import pour ces deux onglets.</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>—</v>
+      </c>
+      <c r="B28" t="str">
+        <v>(saisie à l'écran)</v>
+      </c>
+      <c r="C28" t="str">
         <v>Rendez-vous médicaux</v>
       </c>
-      <c r="D27" t="str">
+      <c r="D28" t="str">
         <v>Santé &amp; Visites → Agenda</v>
       </c>
-      <c r="E27" t="str">
+      <c r="E28" t="str">
         <v>Pas d'import : l'agenda démarre à la mise en service.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E28"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/KIT-REPRISE/00-mode-d-emploi.xlsx
+++ b/KIT-REPRISE/00-mode-d-emploi.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <cols>
     <col min="1" max="1" width="7.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -789,13 +789,13 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C23" t="str">
-        <v>Revues de direction</v>
+        <v>Objectifs santé-sécurité</v>
       </c>
       <c r="D23" t="str">
-        <v>Revue de direction</v>
+        <v>Objectifs santé-sécurité</v>
       </c>
       <c r="E23" t="str">
-        <v>Pas d'import : chaque revue se prépare à l'écran à partir des données reprises.</v>
+        <v>Pas d'import : chaque objectif se fixe à l'écran, sur un indicateur que l'application calcule.</v>
       </c>
     </row>
     <row r="24">
@@ -806,13 +806,13 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C24" t="str">
-        <v>Signalements</v>
+        <v>Revues de direction</v>
       </c>
       <c r="D24" t="str">
-        <v>Signalements</v>
+        <v>Revue de direction</v>
       </c>
       <c r="E24" t="str">
-        <v>Pas d'import : chaque presque-accident se signale à l'écran ; un historique se reprend au Registre AT/MP (type « Presque accident »).</v>
+        <v>Pas d'import : chaque revue se prépare à l'écran à partir des données reprises.</v>
       </c>
     </row>
     <row r="25">
@@ -823,13 +823,13 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C25" t="str">
-        <v>Entreprises extérieures</v>
+        <v>Signalements</v>
       </c>
       <c r="D25" t="str">
-        <v>Entreprises extérieures</v>
+        <v>Signalements</v>
       </c>
       <c r="E25" t="str">
-        <v>Pas d'import : une fiche par intervention.</v>
+        <v>Pas d'import : chaque presque-accident se signale à l'écran ; un historique se reprend au Registre AT/MP (type « Presque accident »).</v>
       </c>
     </row>
     <row r="26">
@@ -840,13 +840,13 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C26" t="str">
-        <v>Base documentaire</v>
+        <v>Entreprises extérieures</v>
       </c>
       <c r="D26" t="str">
-        <v>Base documentaire</v>
+        <v>Entreprises extérieures</v>
       </c>
       <c r="E26" t="str">
-        <v>Pas d'import : fiches et documents se saisissent à l'écran.</v>
+        <v>Pas d'import : une fiche par intervention.</v>
       </c>
     </row>
     <row r="27">
@@ -857,13 +857,13 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C27" t="str">
-        <v>Stock et lavages des EPI</v>
+        <v>Base documentaire</v>
       </c>
       <c r="D27" t="str">
-        <v>EPI &amp; Dotation</v>
+        <v>Base documentaire</v>
       </c>
       <c r="E27" t="str">
-        <v>Pas d'import pour ces deux onglets.</v>
+        <v>Pas d'import : fiches et documents se saisissent à l'écran.</v>
       </c>
     </row>
     <row r="28">
@@ -874,18 +874,35 @@
         <v>(saisie à l'écran)</v>
       </c>
       <c r="C28" t="str">
+        <v>Stock et lavages des EPI</v>
+      </c>
+      <c r="D28" t="str">
+        <v>EPI &amp; Dotation</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Pas d'import pour ces deux onglets.</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>—</v>
+      </c>
+      <c r="B29" t="str">
+        <v>(saisie à l'écran)</v>
+      </c>
+      <c r="C29" t="str">
         <v>Rendez-vous médicaux</v>
       </c>
-      <c r="D28" t="str">
+      <c r="D29" t="str">
         <v>Santé &amp; Visites → Agenda</v>
       </c>
-      <c r="E28" t="str">
+      <c r="E29" t="str">
         <v>Pas d'import : l'agenda démarre à la mise en service.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E29"/>
   </ignoredErrors>
 </worksheet>
 </file>
